--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=20_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=20_without_41.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8764619112817881</v>
+        <v>0.8522682602576751</v>
       </c>
       <c r="C2" t="n">
-        <v>1.857411068061059</v>
+        <v>1.86901908373619</v>
       </c>
       <c r="D2" t="n">
         <v>2.45</v>
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9860605934066596</v>
+        <v>0.9533143364354162</v>
       </c>
       <c r="C3" t="n">
-        <v>1.860217343771138</v>
+        <v>2.004598867209672</v>
       </c>
       <c r="D3" t="n">
         <v>1.8</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9460673212852195</v>
+        <v>0.979265902843205</v>
       </c>
       <c r="C5" t="n">
-        <v>2.195476295175628</v>
+        <v>2.216266367547687</v>
       </c>
       <c r="D5" t="n">
         <v>1.9</v>
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9787423021440009</v>
+        <v>0.9301612847842105</v>
       </c>
       <c r="C6" t="n">
-        <v>1.839873569291389</v>
+        <v>2.032319400203713</v>
       </c>
       <c r="D6" t="n">
         <v>1.75</v>
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9801309649311919</v>
+        <v>0.9777733605690188</v>
       </c>
       <c r="C8" t="n">
-        <v>2.142286976818298</v>
+        <v>1.928659199116467</v>
       </c>
       <c r="D8" t="n">
         <v>2.52</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9457997029318452</v>
+        <v>0.9459141259126976</v>
       </c>
       <c r="C9" t="n">
-        <v>2.909257128941863</v>
+        <v>2.845092431853094</v>
       </c>
       <c r="D9" t="n">
         <v>2.25</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9336628074744417</v>
+        <v>0.9996280029853266</v>
       </c>
       <c r="C10" t="n">
-        <v>1.593769547660082</v>
+        <v>1.697038304773917</v>
       </c>
       <c r="D10" t="n">
         <v>1.75</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9121139869065893</v>
+        <v>0.912113986906589</v>
       </c>
       <c r="C13" t="n">
         <v>1.556345199464247</v>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9399435062965553</v>
+        <v>0.9193864722484825</v>
       </c>
       <c r="C14" t="n">
-        <v>1.476334074259539</v>
+        <v>1.442971511282391</v>
       </c>
       <c r="D14" t="n">
         <v>1.55</v>
@@ -663,7 +663,7 @@
         <v>0.8358527600771796</v>
       </c>
       <c r="C15" t="n">
-        <v>1.595417850252569</v>
+        <v>1.595417850252567</v>
       </c>
       <c r="D15" t="n">
         <v>1.5</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7480387660677363</v>
+        <v>0.7480387660677361</v>
       </c>
       <c r="C17" t="n">
-        <v>2.82818752061558</v>
+        <v>2.828187520615586</v>
       </c>
       <c r="D17" t="n">
         <v>2.8</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9584676582341662</v>
+        <v>0.9584676582341661</v>
       </c>
       <c r="C18" t="n">
         <v>2.315279281947618</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9119447648315009</v>
+        <v>0.9119447648315011</v>
       </c>
       <c r="C19" t="n">
         <v>1.632012528888971</v>
